--- a/request.xlsx
+++ b/request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Eclipse\Projects\restassured_practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0D6E1E0-C451-4E24-9D49-9491988413C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE94BA4-F483-4201-A930-B02DD4483602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{49A4AEF4-1F0B-447A-AF24-F8B45135F705}"/>
   </bookViews>
@@ -74,7 +74,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -82,18 +82,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,32 +428,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A4073E-AA7D-490A-A9D8-9C59B68953F9}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="3"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="C3" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
